--- a/en/downloads/data-excel/1.3.1.d.xlsx
+++ b/en/downloads/data-excel/1.3.1.d.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4421CB4-B534-474F-8C58-6149F8E401B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -35,12 +36,6 @@
     <t>к общей численности пенсионеров, процентов</t>
   </si>
   <si>
-    <t>1.3.1.1g Доля пенсионеров по возрасту, получающих пенсии ниже ПМП</t>
-  </si>
-  <si>
-    <t>1.3.1.1g  ПЖМдан төмөн пенсия алган жаш курагы боюнча пенсионерлердин үлүшү</t>
-  </si>
-  <si>
     <t>Көрсөткүчтөрдүн аталышы</t>
   </si>
   <si>
@@ -50,9 +45,6 @@
     <t>Items</t>
   </si>
   <si>
-    <t>1.3.1.1g Proportion of old-age pensioners receiving pensions below the subsistence level</t>
-  </si>
-  <si>
     <t>Жаш курагы боюнча ПЖМдан төмөн алган пенсионерлердин саны, адам</t>
   </si>
   <si>
@@ -69,12 +61,21 @@
   </si>
   <si>
     <t>to the total number of pensioners, percent</t>
+  </si>
+  <si>
+    <t>1.3.1.d  ПЖМдан төмөн пенсия алган жаш курагы боюнча пенсионерлердин үлүшү</t>
+  </si>
+  <si>
+    <t>1.3.1.d Доля пенсионеров по возрасту, получающих пенсии ниже ПМП</t>
+  </si>
+  <si>
+    <t>1.3.1.d Proportion of old-age pensioners receiving pensions below the subsistence level</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -153,7 +154,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -200,6 +201,17 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -479,8 +491,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:U6"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="35.42578125" style="8" customWidth="1"/>
@@ -489,21 +501,21 @@
     <col min="16" max="16384" width="9.140625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="38.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B1" s="12" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
     </row>
-    <row r="2" spans="1:20" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10"/>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -524,16 +536,17 @@
       <c r="R2" s="15"/>
       <c r="S2" s="15"/>
       <c r="T2" s="15"/>
+      <c r="U2" s="20"/>
     </row>
-    <row r="3" spans="1:20" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>5</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>7</v>
       </c>
       <c r="D3" s="11">
         <v>2007</v>
@@ -586,16 +599,19 @@
       <c r="T3" s="11">
         <v>2023</v>
       </c>
+      <c r="U3" s="18">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="4" spans="1:20" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>0</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="D4" s="2">
         <v>313220</v>
@@ -648,16 +664,19 @@
       <c r="T4" s="2">
         <v>263951</v>
       </c>
+      <c r="U4" s="16">
+        <v>255620</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D5" s="3">
         <v>5.9688636539042399</v>
@@ -710,16 +729,19 @@
       <c r="T5" s="3">
         <v>3.7</v>
       </c>
+      <c r="U5" s="17">
+        <v>3.5103827652043917</v>
+      </c>
     </row>
-    <row r="6" spans="1:20" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:21" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>2</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D6" s="5">
         <v>59.241298307796761</v>
@@ -771,6 +793,9 @@
       </c>
       <c r="T6" s="5">
         <v>32.299999999999997</v>
+      </c>
+      <c r="U6" s="19">
+        <v>30.207203310715151</v>
       </c>
     </row>
   </sheetData>
